--- a/course_enrollment_forms/005_university_course_curriculum_approval_form--course_enrollment_forms.xlsx
+++ b/course_enrollment_forms/005_university_course_curriculum_approval_form--course_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,35 +520,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>page1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>course_curriculum_form</t>
+          <t>University Course Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>course_curriculum_info</t>
+          <t>page2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>curriculum_info</t>
+          <t>Faculty Approval</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>faculty_approval</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>faculty_approvals</t>
+          <t>Course Changes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>Curriculum Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>approval_decision</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>approval_decision</t>
+          <t>Committee Feedback</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>committee_feedback</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>committee_feedback</t>
+          <t>Approval Decision</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Page7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>committee_approvals</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>committee_approvals</t>
+          <t>Faculty Approval 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>approval_decision</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>approval_decision</t>
+          <t>Page10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,16 +750,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>page11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>course_changes</t>
+          <t>Page11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>page12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Committee Approval 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -804,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>faculty_approval_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -821,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>faculty_approval_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -838,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>approval_decision_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>approval_decision_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -872,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>approval_decision_choices</t>
+          <t>page9_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>approval_decision_choices</t>
+          <t>page9_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -898,6 +921,40 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>page12_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>page12_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
